--- a/03_Outputs/De_la_Paz/02_Demografia/demografia.xlsx
+++ b/03_Outputs/De_la_Paz/02_Demografia/demografia.xlsx
@@ -1974,7 +1974,7 @@
         <v>6.51450309082263</v>
       </c>
       <c r="F2" s="82">
-        <v>6.43908905828323</v>
+        <v>6.43908905828322</v>
       </c>
       <c r="G2" s="84">
         <v>37.3963701546045</v>
